--- a/ig/DM-AVRIL-2026/ValueSet-JDV-J121-RolePriseCharge-ENREG.xlsx
+++ b/ig/DM-AVRIL-2026/ValueSet-JDV-J121-RolePriseCharge-ENREG.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="151">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260330120000</t>
+    <t>20260505120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T12:00:00+01:00</t>
+    <t>2026-05-05T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -433,6 +433,30 @@
   </si>
   <si>
     <t>Conseiller conjugal et familial</t>
+  </si>
+  <si>
+    <t>376</t>
+  </si>
+  <si>
+    <t>PADHUE - Médecin</t>
+  </si>
+  <si>
+    <t>377</t>
+  </si>
+  <si>
+    <t>PADHUE - Pharmacien</t>
+  </si>
+  <si>
+    <t>378</t>
+  </si>
+  <si>
+    <t>PADHUE - Sage Femme</t>
+  </si>
+  <si>
+    <t>379</t>
+  </si>
+  <si>
+    <t>PADHUE - Chirurgien Dentiste</t>
   </si>
   <si>
     <t/>
@@ -703,7 +727,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B59"/>
+  <dimension ref="A1:B63"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -1171,15 +1195,47 @@
         <v>140</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>150</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM-AVRIL-2026/ValueSet-JDV-J121-RolePriseCharge-ENREG.xlsx
+++ b/ig/DM-AVRIL-2026/ValueSet-JDV-J121-RolePriseCharge-ENREG.xlsx
@@ -138,7 +138,7 @@
     <t>317</t>
   </si>
   <si>
-    <t>Préparateur en pharmacie (officine)</t>
+    <t>Préparateur en pharmacie</t>
   </si>
   <si>
     <t>319</t>
